--- a/docs/Mapping_casi_uso/trascrizioni/Trascr_Matr_003.xlsx
+++ b/docs/Mapping_casi_uso/trascrizioni/Trascr_Matr_003.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="959" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="973" uniqueCount="187">
   <si>
     <t>Sezione</t>
   </si>
@@ -374,6 +374,12 @@
     <t>flagFirmatario</t>
   </si>
   <si>
+    <t>Età(anni)</t>
+  </si>
+  <si>
+    <t>anni</t>
+  </si>
+  <si>
     <t>Provincia AIRE</t>
   </si>
   <si>
@@ -408,6 +414,9 @@
   </si>
   <si>
     <t>evento.intestatari[1]</t>
+  </si>
+  <si>
+    <t>Età(Anni)</t>
   </si>
   <si>
     <t>Atto Nascita Sposo</t>
@@ -622,7 +631,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H137"/>
+  <dimension ref="A1:H139"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="17.84375" customWidth="true" bestFit="true"/>
@@ -1424,7 +1433,7 @@
         <v>77</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>65</v>
@@ -2039,19 +2048,19 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B62" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="B62" s="2" t="s">
-        <v>64</v>
-      </c>
       <c r="C62" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D62" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E62" s="2" t="s">
         <v>131</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>66</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>10</v>
@@ -2062,19 +2071,19 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>10</v>
@@ -2085,19 +2094,19 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>10</v>
@@ -2108,19 +2117,19 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>10</v>
@@ -2131,19 +2140,19 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>10</v>
@@ -2154,19 +2163,19 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>10</v>
@@ -2177,19 +2186,19 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>10</v>
@@ -2200,19 +2209,19 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>10</v>
@@ -2223,19 +2232,19 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>24</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>10</v>
@@ -2246,19 +2255,19 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>10</v>
@@ -2269,19 +2278,19 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F72" s="2" t="s">
         <v>10</v>
@@ -2292,19 +2301,19 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>10</v>
@@ -2315,19 +2324,19 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F74" s="2" t="s">
         <v>10</v>
@@ -2338,19 +2347,19 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>54</v>
+        <v>89</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F75" s="2" t="s">
         <v>10</v>
@@ -2361,19 +2370,19 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>92</v>
+        <v>54</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F76" s="2" t="s">
         <v>10</v>
@@ -2384,19 +2393,19 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F77" s="2" t="s">
         <v>10</v>
@@ -2407,19 +2416,19 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>10</v>
@@ -2430,19 +2439,19 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F79" s="2" t="s">
         <v>10</v>
@@ -2453,19 +2462,19 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F80" s="2" t="s">
         <v>10</v>
@@ -2476,19 +2485,19 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F81" s="2" t="s">
         <v>10</v>
@@ -2499,19 +2508,19 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F82" s="2" t="s">
         <v>10</v>
@@ -2522,19 +2531,19 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F83" s="2" t="s">
         <v>10</v>
@@ -2545,19 +2554,19 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F84" s="2" t="s">
         <v>10</v>
@@ -2568,19 +2577,19 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F85" s="2" t="s">
         <v>10</v>
@@ -2591,19 +2600,19 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F86" s="2" t="s">
         <v>10</v>
@@ -2614,19 +2623,19 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F87" s="2" t="s">
         <v>10</v>
@@ -2637,19 +2646,19 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>24</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F88" s="2" t="s">
         <v>10</v>
@@ -2660,19 +2669,19 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>24</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F89" s="2" t="s">
         <v>10</v>
@@ -2683,19 +2692,19 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F90" s="2" t="s">
         <v>10</v>
@@ -2706,19 +2715,19 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F91" s="2" t="s">
         <v>10</v>
@@ -2729,19 +2738,19 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F92" s="2" t="s">
         <v>10</v>
@@ -2752,19 +2761,19 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F93" s="2" t="s">
         <v>10</v>
@@ -2775,19 +2784,19 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F94" s="2" t="s">
         <v>10</v>
@@ -2801,16 +2810,16 @@
         <v>132</v>
       </c>
       <c r="B95" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D95" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="C95" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D95" s="2" t="s">
-        <v>134</v>
-      </c>
       <c r="E95" s="2" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="F95" s="2" t="s">
         <v>10</v>
@@ -2824,16 +2833,16 @@
         <v>132</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="F96" s="2" t="s">
         <v>10</v>
@@ -2844,19 +2853,19 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B97" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E97" s="2" t="s">
         <v>138</v>
-      </c>
-      <c r="C97" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D97" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="E97" s="2" t="s">
-        <v>139</v>
       </c>
       <c r="F97" s="2" t="s">
         <v>10</v>
@@ -2867,19 +2876,19 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B98" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E98" s="2" t="s">
         <v>140</v>
-      </c>
-      <c r="C98" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D98" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="E98" s="2" t="s">
-        <v>141</v>
       </c>
       <c r="F98" s="2" t="s">
         <v>10</v>
@@ -2890,19 +2899,19 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B99" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E99" s="2" t="s">
         <v>142</v>
-      </c>
-      <c r="C99" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D99" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="E99" s="2" t="s">
-        <v>143</v>
       </c>
       <c r="F99" s="2" t="s">
         <v>10</v>
@@ -2913,19 +2922,19 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B100" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E100" s="2" t="s">
         <v>144</v>
-      </c>
-      <c r="C100" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D100" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="E100" s="2" t="s">
-        <v>29</v>
       </c>
       <c r="F100" s="2" t="s">
         <v>10</v>
@@ -2936,7 +2945,7 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>145</v>
@@ -2945,7 +2954,7 @@
         <v>9</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>146</v>
@@ -2959,7 +2968,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>147</v>
@@ -2968,10 +2977,10 @@
         <v>9</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F102" s="2" t="s">
         <v>10</v>
@@ -2982,7 +2991,7 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>148</v>
@@ -2991,7 +3000,7 @@
         <v>9</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>149</v>
@@ -3005,7 +3014,7 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>150</v>
@@ -3014,10 +3023,10 @@
         <v>9</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>151</v>
+        <v>32</v>
       </c>
       <c r="F104" s="2" t="s">
         <v>10</v>
@@ -3028,19 +3037,19 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B105" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E105" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="C105" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D105" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="E105" s="2" t="s">
-        <v>153</v>
       </c>
       <c r="F105" s="2" t="s">
         <v>10</v>
@@ -3051,19 +3060,19 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B106" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E106" s="2" t="s">
         <v>154</v>
-      </c>
-      <c r="C106" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D106" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="E106" s="2" t="s">
-        <v>155</v>
       </c>
       <c r="F106" s="2" t="s">
         <v>10</v>
@@ -3074,19 +3083,19 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E107" s="2" t="s">
         <v>156</v>
-      </c>
-      <c r="B107" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="C107" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D107" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="E107" s="2" t="s">
-        <v>135</v>
       </c>
       <c r="F107" s="2" t="s">
         <v>10</v>
@@ -3097,19 +3106,19 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>136</v>
+        <v>157</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>157</v>
+        <v>137</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>137</v>
+        <v>158</v>
       </c>
       <c r="F108" s="2" t="s">
         <v>10</v>
@@ -3120,19 +3129,19 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B109" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="E109" s="2" t="s">
         <v>138</v>
-      </c>
-      <c r="C109" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D109" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="E109" s="2" t="s">
-        <v>139</v>
       </c>
       <c r="F109" s="2" t="s">
         <v>10</v>
@@ -3143,19 +3152,19 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B110" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="E110" s="2" t="s">
         <v>140</v>
-      </c>
-      <c r="C110" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D110" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="E110" s="2" t="s">
-        <v>141</v>
       </c>
       <c r="F110" s="2" t="s">
         <v>10</v>
@@ -3166,19 +3175,19 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B111" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="E111" s="2" t="s">
         <v>142</v>
-      </c>
-      <c r="C111" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D111" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="E111" s="2" t="s">
-        <v>143</v>
       </c>
       <c r="F111" s="2" t="s">
         <v>10</v>
@@ -3189,19 +3198,19 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B112" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="E112" s="2" t="s">
         <v>144</v>
-      </c>
-      <c r="C112" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D112" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="E112" s="2" t="s">
-        <v>29</v>
       </c>
       <c r="F112" s="2" t="s">
         <v>10</v>
@@ -3212,7 +3221,7 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>145</v>
@@ -3221,7 +3230,7 @@
         <v>9</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>146</v>
@@ -3235,7 +3244,7 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>147</v>
@@ -3244,10 +3253,10 @@
         <v>9</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F114" s="2" t="s">
         <v>10</v>
@@ -3258,7 +3267,7 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B115" s="2" t="s">
         <v>148</v>
@@ -3267,7 +3276,7 @@
         <v>9</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>149</v>
@@ -3281,7 +3290,7 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>150</v>
@@ -3290,10 +3299,10 @@
         <v>9</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>151</v>
+        <v>32</v>
       </c>
       <c r="F116" s="2" t="s">
         <v>10</v>
@@ -3304,19 +3313,19 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B117" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="E117" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="C117" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D117" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="E117" s="2" t="s">
-        <v>153</v>
       </c>
       <c r="F117" s="2" t="s">
         <v>10</v>
@@ -3327,19 +3336,19 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B118" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C118" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="E118" s="2" t="s">
         <v>154</v>
-      </c>
-      <c r="C118" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D118" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="E118" s="2" t="s">
-        <v>155</v>
       </c>
       <c r="F118" s="2" t="s">
         <v>10</v>
@@ -3350,19 +3359,19 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>160</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="F119" s="2" t="s">
         <v>10</v>
@@ -3373,19 +3382,19 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>160</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="F120" s="2" t="s">
         <v>10</v>
@@ -3396,19 +3405,19 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>24</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F121" s="2" t="s">
         <v>10</v>
@@ -3419,19 +3428,19 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>24</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F122" s="2" t="s">
         <v>10</v>
@@ -3442,19 +3451,19 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B123" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D123" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="E123" s="2" t="s">
         <v>168</v>
-      </c>
-      <c r="C123" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D123" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="E123" s="2" t="s">
-        <v>169</v>
       </c>
       <c r="F123" s="2" t="s">
         <v>10</v>
@@ -3465,19 +3474,19 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B124" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D124" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="E124" s="2" t="s">
         <v>170</v>
-      </c>
-      <c r="C124" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D124" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="E124" s="2" t="s">
-        <v>171</v>
       </c>
       <c r="F124" s="2" t="s">
         <v>10</v>
@@ -3488,19 +3497,19 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B125" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D125" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="E125" s="2" t="s">
         <v>172</v>
-      </c>
-      <c r="C125" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D125" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="E125" s="2" t="s">
-        <v>173</v>
       </c>
       <c r="F125" s="2" t="s">
         <v>10</v>
@@ -3511,19 +3520,19 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B126" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="E126" s="2" t="s">
         <v>174</v>
-      </c>
-      <c r="C126" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D126" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="E126" s="2" t="s">
-        <v>175</v>
       </c>
       <c r="F126" s="2" t="s">
         <v>10</v>
@@ -3534,19 +3543,19 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B127" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="E127" s="2" t="s">
         <v>176</v>
-      </c>
-      <c r="C127" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D127" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="E127" s="2" t="s">
-        <v>177</v>
       </c>
       <c r="F127" s="2" t="s">
         <v>10</v>
@@ -3557,19 +3566,19 @@
     </row>
     <row r="128">
       <c r="A128" s="2" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>54</v>
+        <v>177</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>55</v>
+        <v>178</v>
       </c>
       <c r="F128" s="2" t="s">
         <v>10</v>
@@ -3580,19 +3589,19 @@
     </row>
     <row r="129">
       <c r="A129" s="2" t="s">
-        <v>178</v>
+        <v>161</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="F129" s="2" t="s">
         <v>10</v>
@@ -3603,19 +3612,19 @@
     </row>
     <row r="130">
       <c r="A130" s="2" t="s">
-        <v>178</v>
+        <v>161</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>166</v>
+        <v>54</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>167</v>
+        <v>55</v>
       </c>
       <c r="F130" s="2" t="s">
         <v>10</v>
@@ -3626,19 +3635,19 @@
     </row>
     <row r="131">
       <c r="A131" s="2" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>24</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F131" s="2" t="s">
         <v>10</v>
@@ -3649,19 +3658,19 @@
     </row>
     <row r="132">
       <c r="A132" s="2" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B132" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C132" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D132" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="E132" s="2" t="s">
         <v>170</v>
-      </c>
-      <c r="C132" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D132" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="E132" s="2" t="s">
-        <v>171</v>
       </c>
       <c r="F132" s="2" t="s">
         <v>10</v>
@@ -3672,19 +3681,19 @@
     </row>
     <row r="133">
       <c r="A133" s="2" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B133" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D133" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="E133" s="2" t="s">
         <v>172</v>
-      </c>
-      <c r="C133" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D133" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="E133" s="2" t="s">
-        <v>173</v>
       </c>
       <c r="F133" s="2" t="s">
         <v>10</v>
@@ -3695,19 +3704,19 @@
     </row>
     <row r="134">
       <c r="A134" s="2" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B134" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C134" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="E134" s="2" t="s">
         <v>174</v>
-      </c>
-      <c r="C134" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D134" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="E134" s="2" t="s">
-        <v>175</v>
       </c>
       <c r="F134" s="2" t="s">
         <v>10</v>
@@ -3718,19 +3727,19 @@
     </row>
     <row r="135">
       <c r="A135" s="2" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B135" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C135" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D135" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="E135" s="2" t="s">
         <v>176</v>
-      </c>
-      <c r="C135" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D135" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="E135" s="2" t="s">
-        <v>177</v>
       </c>
       <c r="F135" s="2" t="s">
         <v>10</v>
@@ -3741,19 +3750,19 @@
     </row>
     <row r="136">
       <c r="A136" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B136" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C136" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D136" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="E136" s="2" t="s">
         <v>178</v>
-      </c>
-      <c r="B136" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="C136" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D136" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="E136" s="2" t="s">
-        <v>181</v>
       </c>
       <c r="F136" s="2" t="s">
         <v>10</v>
@@ -3764,24 +3773,70 @@
     </row>
     <row r="137">
       <c r="A137" s="2" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B137" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C137" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D137" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="C137" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D137" s="2" t="s">
-        <v>179</v>
-      </c>
       <c r="E137" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="F137" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G137" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B138" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="F137" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G137" s="2" t="s">
+      <c r="C138" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D138" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="E138" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="F138" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G138" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B139" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C139" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D139" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="E139" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="F139" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G139" s="2" t="s">
         <v>30</v>
       </c>
     </row>

--- a/docs/Mapping_casi_uso/trascrizioni/Trascr_Matr_003.xlsx
+++ b/docs/Mapping_casi_uso/trascrizioni/Trascr_Matr_003.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="973" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="987" uniqueCount="191">
   <si>
     <t>Sezione</t>
   </si>
@@ -128,10 +128,22 @@
     <t>Dati generali</t>
   </si>
   <si>
+    <t>Formato Data Evento Matrimonio</t>
+  </si>
+  <si>
+    <t>evento.datiEventoMatrimonio</t>
+  </si>
+  <si>
+    <t>idFormatoDataEvento</t>
+  </si>
+  <si>
+    <t>Formato Data Evento Matrimonio - Descrizione</t>
+  </si>
+  <si>
+    <t>formatoDataEvento</t>
+  </si>
+  <si>
     <t>Data Evento Matrimonio</t>
-  </si>
-  <si>
-    <t>evento.datiEventoMatrimonio</t>
   </si>
   <si>
     <t>dataEvento</t>
@@ -631,7 +643,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H139"/>
+  <dimension ref="A1:H141"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="17.84375" customWidth="true" bestFit="true"/>
@@ -1042,7 +1054,7 @@
         <v>38</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>39</v>
@@ -1065,13 +1077,13 @@
         <v>41</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>42</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>43</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>10</v>
@@ -1085,16 +1097,16 @@
         <v>37</v>
       </c>
       <c r="B20" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>45</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>10</v>
@@ -1108,13 +1120,13 @@
         <v>37</v>
       </c>
       <c r="B21" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D21" s="2" t="s">
         <v>46</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>42</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>47</v>
@@ -1137,7 +1149,7 @@
         <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>49</v>
@@ -1160,7 +1172,7 @@
         <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>51</v>
@@ -1183,7 +1195,7 @@
         <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>53</v>
@@ -1206,7 +1218,7 @@
         <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>55</v>
@@ -1226,13 +1238,13 @@
         <v>56</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>58</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>10</v>
@@ -1246,16 +1258,16 @@
         <v>37</v>
       </c>
       <c r="B27" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>59</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>60</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>10</v>
@@ -1269,13 +1281,13 @@
         <v>37</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>24</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>62</v>
@@ -1289,19 +1301,19 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B29" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="C29" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>64</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>66</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>10</v>
@@ -1312,19 +1324,19 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>63</v>
+        <v>37</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>24</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>10</v>
@@ -1335,16 +1347,16 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B31" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D31" s="2" t="s">
         <v>69</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>65</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>70</v>
@@ -1358,7 +1370,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>71</v>
@@ -1367,7 +1379,7 @@
         <v>24</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>72</v>
@@ -1381,7 +1393,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>73</v>
@@ -1390,7 +1402,7 @@
         <v>9</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>74</v>
@@ -1404,16 +1416,16 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>75</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>76</v>
@@ -1427,7 +1439,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>77</v>
@@ -1436,7 +1448,7 @@
         <v>9</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>78</v>
@@ -1450,16 +1462,16 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>79</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>80</v>
@@ -1473,16 +1485,16 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>81</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>82</v>
@@ -1496,16 +1508,16 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>83</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>84</v>
@@ -1519,16 +1531,16 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>85</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>86</v>
@@ -1542,7 +1554,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>87</v>
@@ -1551,7 +1563,7 @@
         <v>9</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>88</v>
@@ -1565,7 +1577,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>89</v>
@@ -1574,7 +1586,7 @@
         <v>9</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>90</v>
@@ -1588,19 +1600,19 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>54</v>
+        <v>91</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>10</v>
@@ -1611,19 +1623,19 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>10</v>
@@ -1634,16 +1646,16 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>94</v>
+        <v>58</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>95</v>
@@ -1657,7 +1669,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>96</v>
@@ -1666,7 +1678,7 @@
         <v>9</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>97</v>
@@ -1680,7 +1692,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>98</v>
@@ -1689,7 +1701,7 @@
         <v>9</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>99</v>
@@ -1703,7 +1715,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>100</v>
@@ -1712,7 +1724,7 @@
         <v>9</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>101</v>
@@ -1726,7 +1738,7 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>102</v>
@@ -1735,7 +1747,7 @@
         <v>9</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>103</v>
@@ -1749,7 +1761,7 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>104</v>
@@ -1758,7 +1770,7 @@
         <v>9</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>105</v>
@@ -1772,7 +1784,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>106</v>
@@ -1781,7 +1793,7 @@
         <v>9</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>107</v>
@@ -1795,7 +1807,7 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>108</v>
@@ -1804,7 +1816,7 @@
         <v>9</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>109</v>
@@ -1818,7 +1830,7 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>110</v>
@@ -1827,7 +1839,7 @@
         <v>9</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>111</v>
@@ -1841,7 +1853,7 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>112</v>
@@ -1850,7 +1862,7 @@
         <v>9</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>113</v>
@@ -1864,16 +1876,16 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>114</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>115</v>
@@ -1887,16 +1899,16 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>116</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>117</v>
@@ -1910,7 +1922,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>118</v>
@@ -1919,7 +1931,7 @@
         <v>24</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>119</v>
@@ -1933,16 +1945,16 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>120</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>121</v>
@@ -1956,16 +1968,16 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>122</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>123</v>
@@ -1979,7 +1991,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>124</v>
@@ -1988,7 +2000,7 @@
         <v>9</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>125</v>
@@ -2002,7 +2014,7 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>126</v>
@@ -2011,7 +2023,7 @@
         <v>9</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>127</v>
@@ -2025,7 +2037,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>128</v>
@@ -2034,7 +2046,7 @@
         <v>9</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>129</v>
@@ -2048,7 +2060,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>130</v>
@@ -2057,7 +2069,7 @@
         <v>9</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>131</v>
@@ -2071,19 +2083,19 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B63" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="B63" s="2" t="s">
-        <v>64</v>
-      </c>
       <c r="C63" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D63" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E63" s="2" t="s">
         <v>133</v>
-      </c>
-      <c r="E63" s="2" t="s">
-        <v>66</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>10</v>
@@ -2094,19 +2106,19 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>132</v>
+        <v>67</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>67</v>
+        <v>134</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>68</v>
+        <v>135</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>10</v>
@@ -2117,16 +2129,16 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>70</v>
@@ -2140,7 +2152,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>71</v>
@@ -2149,7 +2161,7 @@
         <v>24</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>72</v>
@@ -2163,7 +2175,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>73</v>
@@ -2172,7 +2184,7 @@
         <v>9</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>74</v>
@@ -2186,16 +2198,16 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>75</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>76</v>
@@ -2209,7 +2221,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>77</v>
@@ -2218,7 +2230,7 @@
         <v>9</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>78</v>
@@ -2232,16 +2244,16 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>79</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>80</v>
@@ -2255,16 +2267,16 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>81</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>82</v>
@@ -2278,16 +2290,16 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>83</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>84</v>
@@ -2301,16 +2313,16 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>85</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>86</v>
@@ -2324,7 +2336,7 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>87</v>
@@ -2333,7 +2345,7 @@
         <v>9</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>88</v>
@@ -2347,7 +2359,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>89</v>
@@ -2356,7 +2368,7 @@
         <v>9</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>90</v>
@@ -2370,19 +2382,19 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>54</v>
+        <v>91</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F76" s="2" t="s">
         <v>10</v>
@@ -2393,19 +2405,19 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F77" s="2" t="s">
         <v>10</v>
@@ -2416,16 +2428,16 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>94</v>
+        <v>58</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>95</v>
@@ -2439,7 +2451,7 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>96</v>
@@ -2448,7 +2460,7 @@
         <v>9</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>97</v>
@@ -2462,7 +2474,7 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>98</v>
@@ -2471,7 +2483,7 @@
         <v>9</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>99</v>
@@ -2485,7 +2497,7 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>100</v>
@@ -2494,7 +2506,7 @@
         <v>9</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>101</v>
@@ -2508,7 +2520,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>102</v>
@@ -2517,7 +2529,7 @@
         <v>9</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>103</v>
@@ -2531,7 +2543,7 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>104</v>
@@ -2540,7 +2552,7 @@
         <v>9</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>105</v>
@@ -2554,7 +2566,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>106</v>
@@ -2563,7 +2575,7 @@
         <v>9</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>107</v>
@@ -2577,7 +2589,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>108</v>
@@ -2586,7 +2598,7 @@
         <v>9</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>109</v>
@@ -2600,7 +2612,7 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>110</v>
@@ -2609,7 +2621,7 @@
         <v>9</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>111</v>
@@ -2623,7 +2635,7 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>112</v>
@@ -2632,7 +2644,7 @@
         <v>9</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>113</v>
@@ -2646,16 +2658,16 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>114</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>115</v>
@@ -2669,16 +2681,16 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>116</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>117</v>
@@ -2692,7 +2704,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>118</v>
@@ -2701,7 +2713,7 @@
         <v>24</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>119</v>
@@ -2715,16 +2727,16 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>121</v>
@@ -2738,16 +2750,16 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>122</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>123</v>
@@ -2761,16 +2773,16 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>125</v>
@@ -2784,7 +2796,7 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>126</v>
@@ -2793,7 +2805,7 @@
         <v>9</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>127</v>
@@ -2807,7 +2819,7 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>128</v>
@@ -2816,7 +2828,7 @@
         <v>9</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>129</v>
@@ -2830,7 +2842,7 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>130</v>
@@ -2839,7 +2851,7 @@
         <v>9</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>131</v>
@@ -2853,10 +2865,10 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>9</v>
@@ -2865,7 +2877,7 @@
         <v>137</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="F97" s="2" t="s">
         <v>10</v>
@@ -2876,10 +2888,10 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>9</v>
@@ -2888,7 +2900,7 @@
         <v>137</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="F98" s="2" t="s">
         <v>10</v>
@@ -2899,16 +2911,16 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B99" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D99" s="2" t="s">
         <v>141</v>
-      </c>
-      <c r="C99" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D99" s="2" t="s">
-        <v>137</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>142</v>
@@ -2922,7 +2934,7 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>143</v>
@@ -2931,7 +2943,7 @@
         <v>9</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>144</v>
@@ -2945,7 +2957,7 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>145</v>
@@ -2954,7 +2966,7 @@
         <v>9</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>146</v>
@@ -2968,7 +2980,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>147</v>
@@ -2977,10 +2989,10 @@
         <v>9</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>29</v>
+        <v>148</v>
       </c>
       <c r="F102" s="2" t="s">
         <v>10</v>
@@ -2991,19 +3003,19 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F103" s="2" t="s">
         <v>10</v>
@@ -3014,19 +3026,19 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F104" s="2" t="s">
         <v>10</v>
@@ -3037,19 +3049,19 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F105" s="2" t="s">
         <v>10</v>
@@ -3060,19 +3072,19 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>154</v>
+        <v>32</v>
       </c>
       <c r="F106" s="2" t="s">
         <v>10</v>
@@ -3083,7 +3095,7 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>155</v>
@@ -3092,7 +3104,7 @@
         <v>9</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>156</v>
@@ -3106,7 +3118,7 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>157</v>
@@ -3115,7 +3127,7 @@
         <v>9</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>158</v>
@@ -3129,19 +3141,19 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B109" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="B109" s="2" t="s">
-        <v>136</v>
-      </c>
       <c r="C109" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D109" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="E109" s="2" t="s">
         <v>160</v>
-      </c>
-      <c r="E109" s="2" t="s">
-        <v>138</v>
       </c>
       <c r="F109" s="2" t="s">
         <v>10</v>
@@ -3152,19 +3164,19 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>159</v>
+        <v>139</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>139</v>
+        <v>161</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>160</v>
+        <v>141</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
       <c r="F110" s="2" t="s">
         <v>10</v>
@@ -3175,16 +3187,16 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>142</v>
@@ -3198,7 +3210,7 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>143</v>
@@ -3207,7 +3219,7 @@
         <v>9</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>144</v>
@@ -3221,7 +3233,7 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>145</v>
@@ -3230,7 +3242,7 @@
         <v>9</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>146</v>
@@ -3244,7 +3256,7 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>147</v>
@@ -3253,10 +3265,10 @@
         <v>9</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>29</v>
+        <v>148</v>
       </c>
       <c r="F114" s="2" t="s">
         <v>10</v>
@@ -3267,19 +3279,19 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F115" s="2" t="s">
         <v>10</v>
@@ -3290,19 +3302,19 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F116" s="2" t="s">
         <v>10</v>
@@ -3313,19 +3325,19 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F117" s="2" t="s">
         <v>10</v>
@@ -3336,19 +3348,19 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>154</v>
+        <v>32</v>
       </c>
       <c r="F118" s="2" t="s">
         <v>10</v>
@@ -3359,7 +3371,7 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B119" s="2" t="s">
         <v>155</v>
@@ -3368,7 +3380,7 @@
         <v>9</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="E119" s="2" t="s">
         <v>156</v>
@@ -3382,7 +3394,7 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B120" s="2" t="s">
         <v>157</v>
@@ -3391,7 +3403,7 @@
         <v>9</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>158</v>
@@ -3405,19 +3417,19 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="F121" s="2" t="s">
         <v>10</v>
@@ -3428,19 +3440,19 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B122" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="B122" s="2" t="s">
-        <v>165</v>
-      </c>
       <c r="C122" s="2" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="F122" s="2" t="s">
         <v>10</v>
@@ -3451,16 +3463,16 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>24</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>168</v>
@@ -3474,7 +3486,7 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>169</v>
@@ -3483,7 +3495,7 @@
         <v>24</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>170</v>
@@ -3497,16 +3509,16 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B125" s="2" t="s">
         <v>171</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>172</v>
@@ -3520,16 +3532,16 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B126" s="2" t="s">
         <v>173</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>174</v>
@@ -3543,7 +3555,7 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B127" s="2" t="s">
         <v>175</v>
@@ -3552,7 +3564,7 @@
         <v>9</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E127" s="2" t="s">
         <v>176</v>
@@ -3566,7 +3578,7 @@
     </row>
     <row r="128">
       <c r="A128" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B128" s="2" t="s">
         <v>177</v>
@@ -3575,7 +3587,7 @@
         <v>9</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>178</v>
@@ -3589,7 +3601,7 @@
     </row>
     <row r="129">
       <c r="A129" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B129" s="2" t="s">
         <v>179</v>
@@ -3598,7 +3610,7 @@
         <v>9</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>180</v>
@@ -3612,19 +3624,19 @@
     </row>
     <row r="130">
       <c r="A130" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>54</v>
+        <v>181</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>55</v>
+        <v>182</v>
       </c>
       <c r="F130" s="2" t="s">
         <v>10</v>
@@ -3635,19 +3647,19 @@
     </row>
     <row r="131">
       <c r="A131" s="2" t="s">
-        <v>181</v>
+        <v>165</v>
       </c>
       <c r="B131" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C131" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D131" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="C131" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D131" s="2" t="s">
-        <v>182</v>
-      </c>
       <c r="E131" s="2" t="s">
-        <v>168</v>
+        <v>184</v>
       </c>
       <c r="F131" s="2" t="s">
         <v>10</v>
@@ -3658,19 +3670,19 @@
     </row>
     <row r="132">
       <c r="A132" s="2" t="s">
-        <v>181</v>
+        <v>165</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>169</v>
+        <v>58</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>170</v>
+        <v>59</v>
       </c>
       <c r="F132" s="2" t="s">
         <v>10</v>
@@ -3681,7 +3693,7 @@
     </row>
     <row r="133">
       <c r="A133" s="2" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B133" s="2" t="s">
         <v>171</v>
@@ -3690,7 +3702,7 @@
         <v>24</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E133" s="2" t="s">
         <v>172</v>
@@ -3704,16 +3716,16 @@
     </row>
     <row r="134">
       <c r="A134" s="2" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B134" s="2" t="s">
         <v>173</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E134" s="2" t="s">
         <v>174</v>
@@ -3727,16 +3739,16 @@
     </row>
     <row r="135">
       <c r="A135" s="2" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B135" s="2" t="s">
         <v>175</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E135" s="2" t="s">
         <v>176</v>
@@ -3750,7 +3762,7 @@
     </row>
     <row r="136">
       <c r="A136" s="2" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B136" s="2" t="s">
         <v>177</v>
@@ -3759,7 +3771,7 @@
         <v>9</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E136" s="2" t="s">
         <v>178</v>
@@ -3773,7 +3785,7 @@
     </row>
     <row r="137">
       <c r="A137" s="2" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B137" s="2" t="s">
         <v>179</v>
@@ -3782,7 +3794,7 @@
         <v>9</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E137" s="2" t="s">
         <v>180</v>
@@ -3796,19 +3808,19 @@
     </row>
     <row r="138">
       <c r="A138" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B138" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="B138" s="2" t="s">
-        <v>183</v>
-      </c>
       <c r="C138" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D138" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="E138" s="2" t="s">
         <v>182</v>
-      </c>
-      <c r="E138" s="2" t="s">
-        <v>184</v>
       </c>
       <c r="F138" s="2" t="s">
         <v>10</v>
@@ -3819,24 +3831,70 @@
     </row>
     <row r="139">
       <c r="A139" s="2" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B139" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C139" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D139" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="E139" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="F139" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G139" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="C139" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D139" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="E139" s="2" t="s">
+      <c r="B140" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C140" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D140" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="F139" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G139" s="2" t="s">
+      <c r="E140" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="F140" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G140" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B141" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C141" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D141" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="E141" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="F141" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G141" s="2" t="s">
         <v>30</v>
       </c>
     </row>
